--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.14919474095741</v>
+        <v>1.81174414540558</v>
       </c>
       <c r="D2" t="n">
-        <v>10.78504821751715</v>
+        <v>1.752570335346537</v>
       </c>
       <c r="E2" t="n">
-        <v>10.46989370578783</v>
+        <v>1.701357727190523</v>
       </c>
       <c r="F2" t="n">
-        <v>14.26461990446986</v>
+        <v>2.318000734476352</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>5.008919790006411</v>
+        <v>0.8139494658760418</v>
       </c>
       <c r="D3" t="n">
-        <v>49.58214554240831</v>
+        <v>8.05709865064135</v>
       </c>
       <c r="E3" t="n">
-        <v>10.46989370578783</v>
+        <v>1.701357727190523</v>
       </c>
       <c r="F3" t="n">
-        <v>14.26461990446986</v>
+        <v>2.318000734476352</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.57114323441043</v>
+        <v>2.855310775591695</v>
       </c>
       <c r="D4" t="n">
-        <v>35.47869624660341</v>
+        <v>5.765288140073054</v>
       </c>
       <c r="E4" t="n">
-        <v>10.46989370578783</v>
+        <v>1.701357727190523</v>
       </c>
       <c r="F4" t="n">
-        <v>14.26461990446986</v>
+        <v>2.318000734476352</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.90775130070795</v>
+        <v>4.860009586365042</v>
       </c>
       <c r="D5" t="n">
-        <v>45.54221140640606</v>
+        <v>7.400609353540985</v>
       </c>
       <c r="E5" t="n">
-        <v>10.46989370578783</v>
+        <v>1.701357727190523</v>
       </c>
       <c r="F5" t="n">
-        <v>14.26461990446986</v>
+        <v>2.318000734476352</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.38035713279841</v>
+        <v>2.661808034079741</v>
       </c>
       <c r="D6" t="n">
-        <v>25.09677175208117</v>
+        <v>4.078225409713191</v>
       </c>
       <c r="E6" t="n">
-        <v>10.46989370578783</v>
+        <v>1.701357727190523</v>
       </c>
       <c r="F6" t="n">
-        <v>14.26461990446986</v>
+        <v>2.318000734476352</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.5082215395587</v>
+        <v>3.820086000178289</v>
       </c>
       <c r="D7" t="n">
-        <v>40.54052989199725</v>
+        <v>6.587836107449553</v>
       </c>
       <c r="E7" t="n">
-        <v>10.46989370578783</v>
+        <v>1.701357727190523</v>
       </c>
       <c r="F7" t="n">
-        <v>14.26461990446986</v>
+        <v>2.318000734476352</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>13.38763814921282</v>
+        <v>2.175491199247083</v>
       </c>
       <c r="D8" t="n">
-        <v>24.17371125877569</v>
+        <v>3.928228079551049</v>
       </c>
       <c r="E8" t="n">
-        <v>10.46989370578783</v>
+        <v>1.701357727190523</v>
       </c>
       <c r="F8" t="n">
-        <v>14.26461990446986</v>
+        <v>2.318000734476352</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.46332451013696</v>
+        <v>5.112790232897257</v>
       </c>
       <c r="D9" t="n">
-        <v>49.42671517607823</v>
+        <v>8.031841216112712</v>
       </c>
       <c r="E9" t="n">
-        <v>10.46989370578783</v>
+        <v>1.701357727190523</v>
       </c>
       <c r="F9" t="n">
-        <v>14.26461990446986</v>
+        <v>2.318000734476352</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.38610118249122</v>
+        <v>5.262741442154823</v>
       </c>
       <c r="D10" t="n">
-        <v>62.66292774386407</v>
+        <v>10.18272575837791</v>
       </c>
       <c r="E10" t="n">
-        <v>10.46989370578783</v>
+        <v>1.701357727190523</v>
       </c>
       <c r="F10" t="n">
-        <v>14.26461990446986</v>
+        <v>2.318000734476352</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>36.2748776373594</v>
+        <v>5.894667616070903</v>
       </c>
       <c r="D11" t="n">
-        <v>51.97426774401524</v>
+        <v>8.445818508402477</v>
       </c>
       <c r="E11" t="n">
-        <v>10.46989370578783</v>
+        <v>1.701357727190523</v>
       </c>
       <c r="F11" t="n">
-        <v>14.26461990446986</v>
+        <v>2.318000734476352</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>36.86161069824358</v>
+        <v>5.990011738464582</v>
       </c>
       <c r="D12" t="n">
-        <v>44.80210579436751</v>
+        <v>7.280342191584722</v>
       </c>
       <c r="E12" t="n">
-        <v>10.46989370578783</v>
+        <v>1.701357727190523</v>
       </c>
       <c r="F12" t="n">
-        <v>14.26461990446986</v>
+        <v>2.318000734476352</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
